--- a/input/index_Template.xlsx
+++ b/input/index_Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\00069749\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\00069749\Downloads\qPCR_setup_pooling-main (1)\qPCR_setup_pooling-main\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C33D4662-D4E5-4A3D-A45D-B583A9ABDBAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA7BA8D1-7ED6-41F4-BA25-740D26D55232}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{4F2E3ACD-65A3-4781-BB8A-039CB6C2BB4D}"/>
+    <workbookView xWindow="19920" yWindow="-10030" windowWidth="18630" windowHeight="17640" activeTab="6" xr2:uid="{4F2E3ACD-65A3-4781-BB8A-039CB6C2BB4D}"/>
   </bookViews>
   <sheets>
     <sheet name="16SFishD_index" sheetId="2" r:id="rId1"/>
@@ -3966,7 +3966,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3991,6 +3991,7 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4326,13 +4327,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8A3326B-BF0D-427A-A54E-4E662FBCE4AF}">
   <dimension ref="A1:E73"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="36.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -5584,13 +5585,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E93E81D7-7931-4173-9CD4-095D9E7E22B9}">
   <dimension ref="A1:E77"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="42.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.26953125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -6854,15 +6855,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{413307E6-1FDF-4093-8CBD-BEAD28C9F2EA}">
   <dimension ref="A1:L73"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="43.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="37.28515625" customWidth="1"/>
+    <col min="1" max="1" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="43.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.7265625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="37.26953125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
@@ -8257,12 +8258,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5049267-CE4D-4740-8CBF-3E8C01186B1A}">
   <dimension ref="A1:D77"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -9307,13 +9308,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DB72C0C-8AD5-4B47-ADED-C797FDCB901A}">
   <dimension ref="A1:L74"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="18.140625" customWidth="1"/>
-    <col min="3" max="3" width="31.85546875" customWidth="1"/>
-    <col min="4" max="4" width="12.5703125" customWidth="1"/>
-    <col min="11" max="11" width="13.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.28515625" customWidth="1"/>
+    <col min="2" max="2" width="18.1796875" customWidth="1"/>
+    <col min="3" max="3" width="31.81640625" customWidth="1"/>
+    <col min="4" max="4" width="12.54296875" customWidth="1"/>
+    <col min="11" max="11" width="13.7265625" customWidth="1"/>
+    <col min="12" max="12" width="25.26953125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
@@ -10711,12 +10712,12 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35361E15-0365-4022-A696-91565217FD45}">
   <dimension ref="A1:E73"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="44.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -11968,13 +11969,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F74E1F8C-02F9-428A-ADA8-E1659C1A5527}">
   <dimension ref="A1:E73"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -12004,7 +12005,7 @@
       <c r="C2" s="6" t="s">
         <v>1132</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="14" t="s">
         <v>298</v>
       </c>
       <c r="E2" s="1" t="s">
@@ -12021,7 +12022,7 @@
       <c r="C3" s="6" t="s">
         <v>1134</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="14" t="s">
         <v>302</v>
       </c>
       <c r="E3" s="1" t="s">
@@ -12038,7 +12039,7 @@
       <c r="C4" s="6" t="s">
         <v>1136</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="14" t="s">
         <v>306</v>
       </c>
       <c r="E4" s="1" t="s">
@@ -12055,7 +12056,7 @@
       <c r="C5" s="6" t="s">
         <v>1138</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="14" t="s">
         <v>310</v>
       </c>
       <c r="E5" s="1" t="s">
@@ -12072,7 +12073,7 @@
       <c r="C6" s="6" t="s">
         <v>1140</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="14" t="s">
         <v>314</v>
       </c>
       <c r="E6" s="1" t="s">
@@ -12089,7 +12090,7 @@
       <c r="C7" s="6" t="s">
         <v>1142</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="14" t="s">
         <v>318</v>
       </c>
       <c r="E7" s="1" t="s">
@@ -12106,7 +12107,7 @@
       <c r="C8" s="6" t="s">
         <v>1144</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="14" t="s">
         <v>322</v>
       </c>
       <c r="E8" s="1" t="s">
@@ -12123,7 +12124,7 @@
       <c r="C9" s="6" t="s">
         <v>1146</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" s="14" t="s">
         <v>326</v>
       </c>
       <c r="E9" s="1" t="s">
@@ -12140,7 +12141,7 @@
       <c r="C10" s="6" t="s">
         <v>1148</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" s="14" t="s">
         <v>330</v>
       </c>
       <c r="E10" s="1" t="s">
@@ -12157,7 +12158,7 @@
       <c r="C11" s="6" t="s">
         <v>1150</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D11" s="14" t="s">
         <v>334</v>
       </c>
       <c r="E11" s="1" t="s">
@@ -12174,7 +12175,7 @@
       <c r="C12" s="6" t="s">
         <v>1152</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D12" s="14" t="s">
         <v>338</v>
       </c>
       <c r="E12" s="1" t="s">
@@ -12191,7 +12192,7 @@
       <c r="C13" s="6" t="s">
         <v>1154</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D13" s="14" t="s">
         <v>342</v>
       </c>
       <c r="E13" s="1" t="s">
@@ -12208,7 +12209,7 @@
       <c r="C14" s="6" t="s">
         <v>1156</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="D14" s="14" t="s">
         <v>346</v>
       </c>
       <c r="E14" s="1" t="s">
@@ -12225,7 +12226,7 @@
       <c r="C15" s="6" t="s">
         <v>1158</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="D15" s="14" t="s">
         <v>350</v>
       </c>
       <c r="E15" s="1" t="s">
@@ -12242,7 +12243,7 @@
       <c r="C16" s="6" t="s">
         <v>1160</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="D16" s="14" t="s">
         <v>354</v>
       </c>
       <c r="E16" s="1" t="s">
@@ -12259,7 +12260,7 @@
       <c r="C17" s="6" t="s">
         <v>1162</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="D17" s="14" t="s">
         <v>358</v>
       </c>
       <c r="E17" s="1" t="s">
@@ -12276,7 +12277,7 @@
       <c r="C18" s="6" t="s">
         <v>1164</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="D18" s="14" t="s">
         <v>362</v>
       </c>
       <c r="E18" s="1" t="s">
@@ -12293,7 +12294,7 @@
       <c r="C19" s="6" t="s">
         <v>1166</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="D19" s="14" t="s">
         <v>366</v>
       </c>
       <c r="E19" s="1" t="s">
@@ -12310,8 +12311,8 @@
       <c r="C20" s="6" t="s">
         <v>1168</v>
       </c>
-      <c r="D20" s="12" t="s">
-        <v>978</v>
+      <c r="D20" s="14" t="s">
+        <v>370</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>9</v>
@@ -12327,8 +12328,8 @@
       <c r="C21" s="6" t="s">
         <v>1170</v>
       </c>
-      <c r="D21" s="12" t="s">
-        <v>982</v>
+      <c r="D21" s="14" t="s">
+        <v>374</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>9</v>
@@ -12344,8 +12345,8 @@
       <c r="C22" s="6" t="s">
         <v>1172</v>
       </c>
-      <c r="D22" s="12" t="s">
-        <v>986</v>
+      <c r="D22" s="14" t="s">
+        <v>378</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>9</v>
@@ -12361,8 +12362,8 @@
       <c r="C23" s="6" t="s">
         <v>1174</v>
       </c>
-      <c r="D23" s="12" t="s">
-        <v>990</v>
+      <c r="D23" s="14" t="s">
+        <v>382</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>9</v>
@@ -12378,8 +12379,8 @@
       <c r="C24" s="6" t="s">
         <v>1176</v>
       </c>
-      <c r="D24" s="12" t="s">
-        <v>994</v>
+      <c r="D24" s="14" t="s">
+        <v>386</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>9</v>
@@ -12395,8 +12396,8 @@
       <c r="C25" s="6" t="s">
         <v>1178</v>
       </c>
-      <c r="D25" s="12" t="s">
-        <v>998</v>
+      <c r="D25" s="14" t="s">
+        <v>390</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>9</v>
@@ -12412,8 +12413,8 @@
       <c r="C26" s="6" t="s">
         <v>1180</v>
       </c>
-      <c r="D26" s="12" t="s">
-        <v>1002</v>
+      <c r="D26" s="14" t="s">
+        <v>394</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>9</v>
@@ -12429,8 +12430,8 @@
       <c r="C27" s="6" t="s">
         <v>1182</v>
       </c>
-      <c r="D27" s="12" t="s">
-        <v>1006</v>
+      <c r="D27" s="14" t="s">
+        <v>398</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>9</v>
@@ -12446,8 +12447,8 @@
       <c r="C28" s="6" t="s">
         <v>1184</v>
       </c>
-      <c r="D28" s="12" t="s">
-        <v>1010</v>
+      <c r="D28" s="14" t="s">
+        <v>402</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>9</v>
@@ -12463,8 +12464,8 @@
       <c r="C29" s="6" t="s">
         <v>1186</v>
       </c>
-      <c r="D29" s="12" t="s">
-        <v>1014</v>
+      <c r="D29" s="14" t="s">
+        <v>406</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>9</v>
@@ -12480,8 +12481,8 @@
       <c r="C30" s="6" t="s">
         <v>1188</v>
       </c>
-      <c r="D30" s="12" t="s">
-        <v>1018</v>
+      <c r="D30" s="14" t="s">
+        <v>410</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>9</v>
@@ -12497,8 +12498,8 @@
       <c r="C31" s="6" t="s">
         <v>1190</v>
       </c>
-      <c r="D31" s="12" t="s">
-        <v>1022</v>
+      <c r="D31" s="14" t="s">
+        <v>414</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>9</v>
@@ -12514,8 +12515,8 @@
       <c r="C32" s="6" t="s">
         <v>1192</v>
       </c>
-      <c r="D32" s="12" t="s">
-        <v>1026</v>
+      <c r="D32" s="14" t="s">
+        <v>418</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>9</v>
@@ -12531,8 +12532,8 @@
       <c r="C33" s="6" t="s">
         <v>1194</v>
       </c>
-      <c r="D33" s="12" t="s">
-        <v>1030</v>
+      <c r="D33" s="14" t="s">
+        <v>422</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>9</v>
@@ -12548,8 +12549,8 @@
       <c r="C34" s="6" t="s">
         <v>1196</v>
       </c>
-      <c r="D34" s="12" t="s">
-        <v>1034</v>
+      <c r="D34" s="14" t="s">
+        <v>113</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>9</v>
@@ -12565,8 +12566,8 @@
       <c r="C35" s="6" t="s">
         <v>1198</v>
       </c>
-      <c r="D35" s="12" t="s">
-        <v>1038</v>
+      <c r="D35" s="14" t="s">
+        <v>117</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>9</v>
@@ -12582,8 +12583,8 @@
       <c r="C36" s="6" t="s">
         <v>1200</v>
       </c>
-      <c r="D36" s="12" t="s">
-        <v>1042</v>
+      <c r="D36" s="14" t="s">
+        <v>121</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>9</v>
@@ -12599,8 +12600,8 @@
       <c r="C37" s="6" t="s">
         <v>1202</v>
       </c>
-      <c r="D37" s="12" t="s">
-        <v>1046</v>
+      <c r="D37" s="14" t="s">
+        <v>125</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>9</v>
@@ -12616,8 +12617,8 @@
       <c r="C38" s="6" t="s">
         <v>1204</v>
       </c>
-      <c r="D38" s="1" t="s">
-        <v>370</v>
+      <c r="D38" s="14" t="s">
+        <v>129</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>9</v>
@@ -12633,8 +12634,8 @@
       <c r="C39" s="6" t="s">
         <v>1206</v>
       </c>
-      <c r="D39" s="1" t="s">
-        <v>374</v>
+      <c r="D39" s="14" t="s">
+        <v>133</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>9</v>
@@ -12650,8 +12651,8 @@
       <c r="C40" s="6" t="s">
         <v>1208</v>
       </c>
-      <c r="D40" s="1" t="s">
-        <v>378</v>
+      <c r="D40" s="14" t="s">
+        <v>137</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>9</v>
@@ -12667,8 +12668,8 @@
       <c r="C41" s="6" t="s">
         <v>1210</v>
       </c>
-      <c r="D41" s="1" t="s">
-        <v>382</v>
+      <c r="D41" s="14" t="s">
+        <v>141</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>9</v>
@@ -12684,8 +12685,8 @@
       <c r="C42" s="6" t="s">
         <v>1212</v>
       </c>
-      <c r="D42" s="1" t="s">
-        <v>386</v>
+      <c r="D42" s="14" t="s">
+        <v>145</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>9</v>
@@ -12701,8 +12702,8 @@
       <c r="C43" s="6" t="s">
         <v>1214</v>
       </c>
-      <c r="D43" s="1" t="s">
-        <v>390</v>
+      <c r="D43" s="14" t="s">
+        <v>149</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>9</v>
@@ -12718,8 +12719,8 @@
       <c r="C44" s="6" t="s">
         <v>1216</v>
       </c>
-      <c r="D44" s="1" t="s">
-        <v>394</v>
+      <c r="D44" s="14" t="s">
+        <v>456</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>9</v>
@@ -12735,8 +12736,8 @@
       <c r="C45" s="6" t="s">
         <v>1218</v>
       </c>
-      <c r="D45" s="1" t="s">
-        <v>398</v>
+      <c r="D45" s="14" t="s">
+        <v>460</v>
       </c>
       <c r="E45" s="1" t="s">
         <v>9</v>
@@ -12752,8 +12753,8 @@
       <c r="C46" s="6" t="s">
         <v>1220</v>
       </c>
-      <c r="D46" s="1" t="s">
-        <v>402</v>
+      <c r="D46" s="14" t="s">
+        <v>464</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>9</v>
@@ -12769,8 +12770,8 @@
       <c r="C47" s="6" t="s">
         <v>1222</v>
       </c>
-      <c r="D47" s="1" t="s">
-        <v>406</v>
+      <c r="D47" s="14" t="s">
+        <v>468</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>9</v>
@@ -12786,8 +12787,8 @@
       <c r="C48" s="6" t="s">
         <v>1224</v>
       </c>
-      <c r="D48" s="1" t="s">
-        <v>410</v>
+      <c r="D48" s="14" t="s">
+        <v>472</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>9</v>
@@ -12803,8 +12804,8 @@
       <c r="C49" s="6" t="s">
         <v>1226</v>
       </c>
-      <c r="D49" s="1" t="s">
-        <v>414</v>
+      <c r="D49" s="14" t="s">
+        <v>476</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>9</v>
@@ -12820,8 +12821,8 @@
       <c r="C50" s="6" t="s">
         <v>1228</v>
       </c>
-      <c r="D50" s="2" t="s">
-        <v>201</v>
+      <c r="D50" s="14" t="s">
+        <v>480</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>202</v>
@@ -12837,8 +12838,8 @@
       <c r="C51" s="6" t="s">
         <v>1230</v>
       </c>
-      <c r="D51" s="2" t="s">
-        <v>206</v>
+      <c r="D51" s="14" t="s">
+        <v>484</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>202</v>
@@ -12854,8 +12855,8 @@
       <c r="C52" s="6" t="s">
         <v>1232</v>
       </c>
-      <c r="D52" s="2" t="s">
-        <v>210</v>
+      <c r="D52" s="14" t="s">
+        <v>488</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>202</v>
@@ -12871,8 +12872,8 @@
       <c r="C53" s="6" t="s">
         <v>1234</v>
       </c>
-      <c r="D53" s="2" t="s">
-        <v>214</v>
+      <c r="D53" s="14" t="s">
+        <v>492</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>202</v>
@@ -12888,8 +12889,8 @@
       <c r="C54" s="6" t="s">
         <v>1236</v>
       </c>
-      <c r="D54" s="2" t="s">
-        <v>218</v>
+      <c r="D54" s="14" t="s">
+        <v>496</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>202</v>
@@ -12905,8 +12906,8 @@
       <c r="C55" s="6" t="s">
         <v>1238</v>
       </c>
-      <c r="D55" s="2" t="s">
-        <v>222</v>
+      <c r="D55" s="14" t="s">
+        <v>500</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>202</v>
@@ -12922,8 +12923,8 @@
       <c r="C56" s="6" t="s">
         <v>1240</v>
       </c>
-      <c r="D56" s="2" t="s">
-        <v>226</v>
+      <c r="D56" s="14" t="s">
+        <v>504</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>202</v>
@@ -12939,8 +12940,8 @@
       <c r="C57" s="6" t="s">
         <v>1242</v>
       </c>
-      <c r="D57" s="2" t="s">
-        <v>230</v>
+      <c r="D57" s="14" t="s">
+        <v>508</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>202</v>
@@ -12956,8 +12957,8 @@
       <c r="C58" s="6" t="s">
         <v>1244</v>
       </c>
-      <c r="D58" s="2" t="s">
-        <v>480</v>
+      <c r="D58" s="14" t="s">
+        <v>512</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>202</v>
@@ -12973,8 +12974,8 @@
       <c r="C59" s="6" t="s">
         <v>1246</v>
       </c>
-      <c r="D59" s="2" t="s">
-        <v>484</v>
+      <c r="D59" s="14" t="s">
+        <v>516</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>202</v>
@@ -12990,8 +12991,8 @@
       <c r="C60" s="6" t="s">
         <v>1248</v>
       </c>
-      <c r="D60" s="2" t="s">
-        <v>488</v>
+      <c r="D60" s="14" t="s">
+        <v>520</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>202</v>
@@ -13007,8 +13008,8 @@
       <c r="C61" s="6" t="s">
         <v>1250</v>
       </c>
-      <c r="D61" s="2" t="s">
-        <v>492</v>
+      <c r="D61" s="14" t="s">
+        <v>524</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>202</v>
@@ -13024,8 +13025,8 @@
       <c r="C62" s="6" t="s">
         <v>1252</v>
       </c>
-      <c r="D62" s="2" t="s">
-        <v>496</v>
+      <c r="D62" s="14" t="s">
+        <v>528</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>202</v>
@@ -13041,8 +13042,8 @@
       <c r="C63" s="6" t="s">
         <v>1254</v>
       </c>
-      <c r="D63" s="2" t="s">
-        <v>500</v>
+      <c r="D63" s="14" t="s">
+        <v>532</v>
       </c>
       <c r="E63" s="1" t="s">
         <v>202</v>
@@ -13058,8 +13059,8 @@
       <c r="C64" s="6" t="s">
         <v>1256</v>
       </c>
-      <c r="D64" s="2" t="s">
-        <v>504</v>
+      <c r="D64" s="14" t="s">
+        <v>536</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>202</v>
@@ -13075,8 +13076,8 @@
       <c r="C65" s="6" t="s">
         <v>1258</v>
       </c>
-      <c r="D65" s="2" t="s">
-        <v>508</v>
+      <c r="D65" s="14" t="s">
+        <v>540</v>
       </c>
       <c r="E65" s="1" t="s">
         <v>202</v>
@@ -13092,8 +13093,8 @@
       <c r="C66" s="6" t="s">
         <v>1260</v>
       </c>
-      <c r="D66" s="2" t="s">
-        <v>512</v>
+      <c r="D66" s="14" t="s">
+        <v>544</v>
       </c>
       <c r="E66" s="1" t="s">
         <v>202</v>
@@ -13109,8 +13110,8 @@
       <c r="C67" s="6" t="s">
         <v>1262</v>
       </c>
-      <c r="D67" s="2" t="s">
-        <v>516</v>
+      <c r="D67" s="14" t="s">
+        <v>548</v>
       </c>
       <c r="E67" s="1" t="s">
         <v>202</v>
@@ -13126,8 +13127,8 @@
       <c r="C68" s="6" t="s">
         <v>1264</v>
       </c>
-      <c r="D68" s="13" t="s">
-        <v>1110</v>
+      <c r="D68" s="14" t="s">
+        <v>552</v>
       </c>
       <c r="E68" s="1" t="s">
         <v>202</v>
@@ -13143,8 +13144,8 @@
       <c r="C69" s="6" t="s">
         <v>1266</v>
       </c>
-      <c r="D69" s="13" t="s">
-        <v>1114</v>
+      <c r="D69" s="14" t="s">
+        <v>556</v>
       </c>
       <c r="E69" s="1" t="s">
         <v>202</v>
@@ -13160,8 +13161,8 @@
       <c r="C70" s="6" t="s">
         <v>1268</v>
       </c>
-      <c r="D70" s="13" t="s">
-        <v>1118</v>
+      <c r="D70" s="14" t="s">
+        <v>560</v>
       </c>
       <c r="E70" s="1" t="s">
         <v>202</v>
@@ -13177,8 +13178,8 @@
       <c r="C71" s="6" t="s">
         <v>1270</v>
       </c>
-      <c r="D71" s="13" t="s">
-        <v>1122</v>
+      <c r="D71" s="14" t="s">
+        <v>564</v>
       </c>
       <c r="E71" s="1" t="s">
         <v>202</v>
@@ -13194,8 +13195,8 @@
       <c r="C72" s="6" t="s">
         <v>1272</v>
       </c>
-      <c r="D72" s="13" t="s">
-        <v>1126</v>
+      <c r="D72" s="14" t="s">
+        <v>274</v>
       </c>
       <c r="E72" s="1" t="s">
         <v>202</v>
@@ -13211,8 +13212,8 @@
       <c r="C73" s="6" t="s">
         <v>1274</v>
       </c>
-      <c r="D73" s="13" t="s">
-        <v>1130</v>
+      <c r="D73" s="14" t="s">
+        <v>278</v>
       </c>
       <c r="E73" s="1" t="s">
         <v>202</v>
@@ -13225,12 +13226,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8776adc8-282a-4073-b44b-e3b5ad797728">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="e19eda2f-2a61-44e3-a391-8f02abd9f5ab" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -13475,20 +13478,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8776adc8-282a-4073-b44b-e3b5ad797728">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="e19eda2f-2a61-44e3-a391-8f02abd9f5ab" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B9FCAA8-CD1F-49A3-8FC1-2BC65AC36FA3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E6E1250-7A19-4909-AB3F-A88FCBAC8A78}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="8776adc8-282a-4073-b44b-e3b5ad797728"/>
+    <ds:schemaRef ds:uri="e19eda2f-2a61-44e3-a391-8f02abd9f5ab"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -13513,12 +13517,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E6E1250-7A19-4909-AB3F-A88FCBAC8A78}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B9FCAA8-CD1F-49A3-8FC1-2BC65AC36FA3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="8776adc8-282a-4073-b44b-e3b5ad797728"/>
-    <ds:schemaRef ds:uri="e19eda2f-2a61-44e3-a391-8f02abd9f5ab"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>